--- a/samples/exports/SAMPLE_submission_2_fictional_partial.xlsx
+++ b/samples/exports/SAMPLE_submission_2_fictional_partial.xlsx
@@ -472,12 +472,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Owner (role or staff name)</t>
+          <t>Owner (name and position)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Reviewer</t>
+          <t>Reviewer (name and position)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -670,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>AUD-20261022-60E5BD</t>
+          <t>AUD-20261022-9C6EB9</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22T05:29:28+00:00</t>
+          <t>2026-10-22T05:51:17+00:00</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Physiotherapist: Person (staff name or job title) Head Physiotherapist; Deputy / cover Physiotherapist 2; Reporting responsibilities Rehab board</t>
+          <t>Physiotherapist: Name Head Physiotherapist; Deputy / cover (name and position) Physiotherapist 2; Reporting responsibilities Rehab board</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Who prepares the daily report? (role)</t>
+          <t>Names and positions of the people who provide it</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Head Physiotherapist</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -880,29 +880,29 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Who reviews it before it is shared? (role, or 'nobody')</t>
+          <t>Who prepares the daily report? (name and position)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Jo Sample - Head Physiotherapist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>4. Timing</t>
+          <t>3. Who provides, prepares and reviews the daily report</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>When is the information usually entered?</t>
+          <t>Who reviews it before it is shared? (name and position, or 'nobody')</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -914,29 +914,29 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>When should the report be ready?</t>
+          <t>When is the information usually entered?</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Varies</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>5. The daily dashboard</t>
+          <t>4. Timing</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Which information should be visible at the top of the daily dashboard? Choose up to three.</t>
+          <t>When should the report be ready?</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Players in rehabilitation; Other: Return-to-training steps</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>What should the daily medical comment communicate?</t>
+          <t>Which information should be visible at the top of the daily dashboard? Choose up to three.</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Players in rehabilitation; Other: Return-to-training steps</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Optional comment on the medical comment format</t>
+          <t>What should the daily medical comment communicate?</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>What does the doctor need the dashboard to show?</t>
+          <t>Optional comment on the medical comment format</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>What does the physical coach need the dashboard to show?</t>
+          <t>What does the doctor need the dashboard to show?</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Rehab group size for the day.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1016,24 +1016,24 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>What does the coach need the dashboard to show?</t>
+          <t>What does the physical coach need the dashboard to show?</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rehab group size for the day.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>6. Counts and definitions</t>
+          <t>5. The daily dashboard</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Which counts or definitions need to be clearer?</t>
+          <t>What does the coach need the dashboard to show?</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Briefly, how are these counted today? (optional)</t>
+          <t>Which counts or definitions need to be clearer?</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>7. Storage and sharing</t>
+          <t>6. Counts and definitions</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Where are the report and its source files stored?</t>
+          <t>Briefly, how are these counted today? (optional)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Printed copies; Other: Whiteboard in the medical room</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>How is the report shared?</t>
+          <t>Where are the report and its source files stored?</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Printed copies; Other: Whiteboard in the medical room</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Optional comment</t>
+          <t>How is the report shared?</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1113,34 +1113,34 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>8. Biggest improvement</t>
+          <t>7. Storage and sharing</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>What one change would save the department the most time, or improve the report the most?</t>
+          <t>Optional comment</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Stop keeping the whiteboard and the spreadsheet in parallel.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>9. Prototype feedback</t>
+          <t>8. Biggest improvement</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Who should review the first dashboard prototype?</t>
+          <t>What one change would save the department the most time, or improve the report the most?</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Stop keeping the whiteboard and the spreadsheet in parallel.</t>
         </is>
       </c>
     </row>
@@ -1152,10 +1152,44 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
+          <t>Who should review the first dashboard prototype?</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>9. Prototype feedback</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Names and positions of the reviewers</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>9. Prototype feedback</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>Optional comment (e.g. best time for a 20-minute review)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Test submission 2 - fictional, partial.</t>
         </is>

--- a/samples/exports/SAMPLE_submission_2_fictional_partial.xlsx
+++ b/samples/exports/SAMPLE_submission_2_fictional_partial.xlsx
@@ -670,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>AUD-20261022-9C6EB9</t>
+          <t>AUD-20261022-9CC92C</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22T05:51:17+00:00</t>
+          <t>2026-10-22T08:32:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1141,57 +1141,6 @@
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Stop keeping the whiteboard and the spreadsheet in parallel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>9. Prototype feedback</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Who should review the first dashboard prototype?</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>9. Prototype feedback</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Names and positions of the reviewers</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>9. Prototype feedback</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Optional comment (e.g. best time for a 20-minute review)</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Test submission 2 - fictional, partial.</t>
         </is>
       </c>
     </row>
